--- a/Docs/assets to import - final from logistic Akkar.xlsx
+++ b/Docs/assets to import - final from logistic Akkar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\logistic\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03639B2F-A52C-44C5-8212-9FE0B4472619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A36DAF-CB9F-47F4-97DE-88F03280E0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-36" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3961" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4169" uniqueCount="280">
   <si>
     <t>Furniture</t>
   </si>
@@ -843,6 +843,42 @@
   </si>
   <si>
     <t>colored Printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owned By </t>
+  </si>
+  <si>
+    <t>B&amp;Z</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Bartolini</t>
+  </si>
+  <si>
+    <t>AK-26-02-06</t>
+  </si>
+  <si>
+    <t>16/3/2026</t>
+  </si>
+  <si>
+    <t>16/3/2027</t>
+  </si>
+  <si>
+    <t>01.03.08</t>
+  </si>
+  <si>
+    <t>MAF</t>
+  </si>
+  <si>
+    <t>Electric Heater 2400 w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B&amp;Z </t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W300"/>
+  <dimension ref="A1:X300"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1355,7 +1391,7 @@
     <col min="20" max="20" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1425,8 +1461,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1496,8 +1535,11 @@
       <c r="W2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1567,8 +1609,11 @@
       <c r="W3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1638,8 +1683,11 @@
       <c r="W4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1709,8 +1757,11 @@
       <c r="W5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1780,8 +1831,11 @@
       <c r="W6" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1851,8 +1905,11 @@
       <c r="W7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1922,8 +1979,11 @@
       <c r="W8" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1993,8 +2053,11 @@
       <c r="W9" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2064,8 +2127,11 @@
       <c r="W10" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2135,8 +2201,11 @@
       <c r="W11" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2206,8 +2275,11 @@
       <c r="W12" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2277,8 +2349,11 @@
       <c r="W13" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2348,8 +2423,11 @@
       <c r="W14" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2419,8 +2497,11 @@
       <c r="W15" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2490,8 +2571,11 @@
       <c r="W16" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2561,8 +2645,11 @@
       <c r="W17" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X17" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2632,8 +2719,11 @@
       <c r="W18" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X18" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2703,8 +2793,11 @@
       <c r="W19" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X19" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2774,8 +2867,11 @@
       <c r="W20" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X20" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2845,8 +2941,11 @@
       <c r="W21" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X21" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2916,8 +3015,11 @@
       <c r="W22" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X22" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2987,8 +3089,11 @@
       <c r="W23" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X23" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3058,8 +3163,11 @@
       <c r="W24" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X24" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3129,8 +3237,11 @@
       <c r="W25" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X25" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>28</v>
       </c>
@@ -3200,8 +3311,11 @@
       <c r="W26" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X26" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>29</v>
       </c>
@@ -3271,8 +3385,11 @@
       <c r="W27" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X27" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>30</v>
       </c>
@@ -3342,8 +3459,11 @@
       <c r="W28" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X28" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>31</v>
       </c>
@@ -3413,8 +3533,11 @@
       <c r="W29" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X29" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>32</v>
       </c>
@@ -3484,8 +3607,11 @@
       <c r="W30" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>33</v>
       </c>
@@ -3555,8 +3681,11 @@
       <c r="W31" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X31" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>34</v>
       </c>
@@ -3626,8 +3755,11 @@
       <c r="W32" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X32" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>35</v>
       </c>
@@ -3697,8 +3829,11 @@
       <c r="W33" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>36</v>
       </c>
@@ -3768,8 +3903,11 @@
       <c r="W34" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X34" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>37</v>
       </c>
@@ -3839,8 +3977,11 @@
       <c r="W35" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X35" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>38</v>
       </c>
@@ -3910,8 +4051,11 @@
       <c r="W36" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X36" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>39</v>
       </c>
@@ -3981,8 +4125,11 @@
       <c r="W37" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X37" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>40</v>
       </c>
@@ -4052,8 +4199,11 @@
       <c r="W38" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X38" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>41</v>
       </c>
@@ -4123,8 +4273,11 @@
       <c r="W39" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X39" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>42</v>
       </c>
@@ -4194,8 +4347,11 @@
       <c r="W40" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X40" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>43</v>
       </c>
@@ -4265,8 +4421,11 @@
       <c r="W41" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X41" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>44</v>
       </c>
@@ -4336,8 +4495,11 @@
       <c r="W42" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X42" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>45</v>
       </c>
@@ -4407,8 +4569,11 @@
       <c r="W43" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X43" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>46</v>
       </c>
@@ -4478,8 +4643,11 @@
       <c r="W44" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X44" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>47</v>
       </c>
@@ -4549,8 +4717,11 @@
       <c r="W45" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X45" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>48</v>
       </c>
@@ -4620,8 +4791,11 @@
       <c r="W46" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X46" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>49</v>
       </c>
@@ -4691,8 +4865,11 @@
       <c r="W47" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X47" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>50</v>
       </c>
@@ -4762,8 +4939,11 @@
       <c r="W48" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X48" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>51</v>
       </c>
@@ -4833,8 +5013,11 @@
       <c r="W49" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X49" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>52</v>
       </c>
@@ -4904,8 +5087,11 @@
       <c r="W50" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X50" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>53</v>
       </c>
@@ -4975,8 +5161,11 @@
       <c r="W51" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X51" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>54</v>
       </c>
@@ -5046,8 +5235,11 @@
       <c r="W52" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X52" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>55</v>
       </c>
@@ -5117,8 +5309,11 @@
       <c r="W53" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X53" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>56</v>
       </c>
@@ -5188,8 +5383,11 @@
       <c r="W54" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X54" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>57</v>
       </c>
@@ -5259,8 +5457,11 @@
       <c r="W55" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X55" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>58</v>
       </c>
@@ -5330,8 +5531,11 @@
       <c r="W56" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X56" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>59</v>
       </c>
@@ -5401,8 +5605,11 @@
       <c r="W57" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X57" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>60</v>
       </c>
@@ -5472,8 +5679,11 @@
       <c r="W58" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X58" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>61</v>
       </c>
@@ -5543,8 +5753,11 @@
       <c r="W59" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X59" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>62</v>
       </c>
@@ -5614,8 +5827,11 @@
       <c r="W60" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X60" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>63</v>
       </c>
@@ -5685,8 +5901,11 @@
       <c r="W61" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X61" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>64</v>
       </c>
@@ -5756,8 +5975,11 @@
       <c r="W62" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X62" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>67</v>
       </c>
@@ -5827,8 +6049,11 @@
       <c r="W63" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X63" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>68</v>
       </c>
@@ -5898,8 +6123,11 @@
       <c r="W64" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X64" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>74</v>
       </c>
@@ -5969,8 +6197,11 @@
       <c r="W65" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X65" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>89</v>
       </c>
@@ -6040,8 +6271,11 @@
       <c r="W66" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X66" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>90</v>
       </c>
@@ -6111,8 +6345,11 @@
       <c r="W67" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X67" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>91</v>
       </c>
@@ -6182,8 +6419,11 @@
       <c r="W68" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X68" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>92</v>
       </c>
@@ -6253,8 +6493,11 @@
       <c r="W69" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X69" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>93</v>
       </c>
@@ -6324,8 +6567,11 @@
       <c r="W70" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X70" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>101</v>
       </c>
@@ -6395,8 +6641,11 @@
       <c r="W71" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X71" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>102</v>
       </c>
@@ -6466,8 +6715,11 @@
       <c r="W72" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X72" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>103</v>
       </c>
@@ -6537,8 +6789,11 @@
       <c r="W73" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X73" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>104</v>
       </c>
@@ -6608,8 +6863,11 @@
       <c r="W74" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X74" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>105</v>
       </c>
@@ -6679,8 +6937,11 @@
       <c r="W75" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X75" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>106</v>
       </c>
@@ -6750,8 +7011,11 @@
       <c r="W76" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X76" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>107</v>
       </c>
@@ -6821,8 +7085,11 @@
       <c r="W77" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X77" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>108</v>
       </c>
@@ -6892,8 +7159,11 @@
       <c r="W78" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X78" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>109</v>
       </c>
@@ -6963,8 +7233,11 @@
       <c r="W79" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X79" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>110</v>
       </c>
@@ -7034,8 +7307,11 @@
       <c r="W80" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X80" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>111</v>
       </c>
@@ -7105,8 +7381,11 @@
       <c r="W81" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X81" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>112</v>
       </c>
@@ -7176,8 +7455,11 @@
       <c r="W82" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X82" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>113</v>
       </c>
@@ -7247,8 +7529,11 @@
       <c r="W83" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X83" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>114</v>
       </c>
@@ -7318,8 +7603,11 @@
       <c r="W84" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X84" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>115</v>
       </c>
@@ -7389,8 +7677,11 @@
       <c r="W85" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X85" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>116</v>
       </c>
@@ -7460,8 +7751,11 @@
       <c r="W86" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X86" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>117</v>
       </c>
@@ -7531,8 +7825,11 @@
       <c r="W87" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X87" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>118</v>
       </c>
@@ -7602,8 +7899,11 @@
       <c r="W88" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X88" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>119</v>
       </c>
@@ -7673,8 +7973,11 @@
       <c r="W89" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X89" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>120</v>
       </c>
@@ -7744,8 +8047,11 @@
       <c r="W90" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X90" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>121</v>
       </c>
@@ -7815,8 +8121,11 @@
       <c r="W91" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X91" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>122</v>
       </c>
@@ -7886,8 +8195,11 @@
       <c r="W92" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X92" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>123</v>
       </c>
@@ -7957,8 +8269,11 @@
       <c r="W93" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X93" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>124</v>
       </c>
@@ -8028,8 +8343,11 @@
       <c r="W94" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X94" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>125</v>
       </c>
@@ -8099,8 +8417,11 @@
       <c r="W95" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X95" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>126</v>
       </c>
@@ -8170,8 +8491,11 @@
       <c r="W96" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X96" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>127</v>
       </c>
@@ -8241,8 +8565,11 @@
       <c r="W97" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X97" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>128</v>
       </c>
@@ -8312,8 +8639,11 @@
       <c r="W98" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X98" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>129</v>
       </c>
@@ -8383,8 +8713,11 @@
       <c r="W99" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X99" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>130</v>
       </c>
@@ -8454,8 +8787,11 @@
       <c r="W100" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X100" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>131</v>
       </c>
@@ -8525,8 +8861,11 @@
       <c r="W101" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X101" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>132</v>
       </c>
@@ -8596,8 +8935,11 @@
       <c r="W102" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X102" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>133</v>
       </c>
@@ -8667,8 +9009,11 @@
       <c r="W103" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X103" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>134</v>
       </c>
@@ -8738,8 +9083,11 @@
       <c r="W104" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X104" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>135</v>
       </c>
@@ -8809,8 +9157,11 @@
       <c r="W105" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X105" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>136</v>
       </c>
@@ -8880,8 +9231,11 @@
       <c r="W106" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X106" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>137</v>
       </c>
@@ -8951,8 +9305,11 @@
       <c r="W107" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X107" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>138</v>
       </c>
@@ -9022,8 +9379,11 @@
       <c r="W108" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X108" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>139</v>
       </c>
@@ -9093,8 +9453,11 @@
       <c r="W109" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X109" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>140</v>
       </c>
@@ -9164,8 +9527,11 @@
       <c r="W110" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X110" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>141</v>
       </c>
@@ -9235,8 +9601,11 @@
       <c r="W111" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X111" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>142</v>
       </c>
@@ -9306,8 +9675,11 @@
       <c r="W112" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X112" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>143</v>
       </c>
@@ -9377,8 +9749,11 @@
       <c r="W113" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X113" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>144</v>
       </c>
@@ -9448,8 +9823,11 @@
       <c r="W114" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X114" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>145</v>
       </c>
@@ -9519,8 +9897,11 @@
       <c r="W115" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X115" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>146</v>
       </c>
@@ -9590,8 +9971,11 @@
       <c r="W116" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X116" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>147</v>
       </c>
@@ -9661,8 +10045,11 @@
       <c r="W117" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X117" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>148</v>
       </c>
@@ -9732,8 +10119,11 @@
       <c r="W118" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X118" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>149</v>
       </c>
@@ -9803,8 +10193,11 @@
       <c r="W119" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X119" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>150</v>
       </c>
@@ -9874,8 +10267,11 @@
       <c r="W120" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X120" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>151</v>
       </c>
@@ -9945,8 +10341,11 @@
       <c r="W121" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X121" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>152</v>
       </c>
@@ -10016,8 +10415,11 @@
       <c r="W122" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X122" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>153</v>
       </c>
@@ -10087,8 +10489,11 @@
       <c r="W123" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X123" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>156</v>
       </c>
@@ -10158,8 +10563,11 @@
       <c r="W124" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X124" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>157</v>
       </c>
@@ -10229,8 +10637,11 @@
       <c r="W125" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X125" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>158</v>
       </c>
@@ -10300,8 +10711,11 @@
       <c r="W126" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X126" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>159</v>
       </c>
@@ -10371,8 +10785,11 @@
       <c r="W127" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X127" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B128" s="4"/>
       <c r="K128" s="5"/>
       <c r="L128" s="2"/>
@@ -10387,8 +10804,9 @@
       <c r="U128" s="2"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
-    </row>
-    <row r="129" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X128" s="2"/>
+    </row>
+    <row r="129" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B129" s="4"/>
       <c r="K129" s="5"/>
       <c r="L129" s="2"/>
@@ -10403,8 +10821,9 @@
       <c r="U129" s="2"/>
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
-    </row>
-    <row r="130" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X129" s="2"/>
+    </row>
+    <row r="130" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B130" s="4"/>
       <c r="K130" s="5"/>
       <c r="L130" s="2"/>
@@ -10419,8 +10838,9 @@
       <c r="U130" s="2"/>
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
-    </row>
-    <row r="131" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X130" s="2"/>
+    </row>
+    <row r="131" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B131" s="4"/>
       <c r="K131" s="5"/>
       <c r="L131" s="2"/>
@@ -10435,8 +10855,9 @@
       <c r="U131" s="2"/>
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
-    </row>
-    <row r="132" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X131" s="2"/>
+    </row>
+    <row r="132" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B132" s="4"/>
       <c r="K132" s="5"/>
       <c r="L132" s="2"/>
@@ -10451,8 +10872,9 @@
       <c r="U132" s="2"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-    </row>
-    <row r="133" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X132" s="2"/>
+    </row>
+    <row r="133" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B133" s="4"/>
       <c r="K133" s="5"/>
       <c r="L133" s="2"/>
@@ -10467,8 +10889,9 @@
       <c r="U133" s="2"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-    </row>
-    <row r="134" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X133" s="2"/>
+    </row>
+    <row r="134" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B134" s="4"/>
       <c r="K134" s="5"/>
       <c r="L134" s="2"/>
@@ -10483,8 +10906,9 @@
       <c r="U134" s="2"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-    </row>
-    <row r="135" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X134" s="2"/>
+    </row>
+    <row r="135" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B135" s="4"/>
       <c r="K135" s="5"/>
       <c r="L135" s="2"/>
@@ -10499,8 +10923,9 @@
       <c r="U135" s="2"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-    </row>
-    <row r="136" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X135" s="2"/>
+    </row>
+    <row r="136" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B136" s="4"/>
       <c r="K136" s="5"/>
       <c r="L136" s="2"/>
@@ -10515,8 +10940,9 @@
       <c r="U136" s="2"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-    </row>
-    <row r="137" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X136" s="2"/>
+    </row>
+    <row r="137" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B137" s="4"/>
       <c r="K137" s="5"/>
       <c r="L137" s="2"/>
@@ -10531,8 +10957,9 @@
       <c r="U137" s="2"/>
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
-    </row>
-    <row r="138" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X137" s="2"/>
+    </row>
+    <row r="138" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B138" s="4"/>
       <c r="K138" s="5"/>
       <c r="L138" s="2"/>
@@ -10547,8 +10974,9 @@
       <c r="U138" s="2"/>
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
-    </row>
-    <row r="139" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X138" s="2"/>
+    </row>
+    <row r="139" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B139" s="4"/>
       <c r="K139" s="5"/>
       <c r="L139" s="2"/>
@@ -10563,8 +10991,9 @@
       <c r="U139" s="2"/>
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
-    </row>
-    <row r="140" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X139" s="2"/>
+    </row>
+    <row r="140" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B140" s="4"/>
       <c r="K140" s="5"/>
       <c r="L140" s="2"/>
@@ -10579,8 +11008,9 @@
       <c r="U140" s="2"/>
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
-    </row>
-    <row r="141" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X140" s="2"/>
+    </row>
+    <row r="141" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B141" s="4"/>
       <c r="K141" s="5"/>
       <c r="L141" s="2"/>
@@ -10595,8 +11025,9 @@
       <c r="U141" s="2"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-    </row>
-    <row r="142" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X141" s="2"/>
+    </row>
+    <row r="142" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B142" s="4"/>
       <c r="K142" s="5"/>
       <c r="L142" s="2"/>
@@ -10611,8 +11042,9 @@
       <c r="U142" s="2"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-    </row>
-    <row r="143" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X142" s="2"/>
+    </row>
+    <row r="143" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B143" s="4"/>
       <c r="K143" s="5"/>
       <c r="L143" s="2"/>
@@ -10627,8 +11059,9 @@
       <c r="U143" s="2"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-    </row>
-    <row r="144" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X143" s="2"/>
+    </row>
+    <row r="144" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B144" s="4"/>
       <c r="K144" s="5"/>
       <c r="L144" s="2"/>
@@ -10643,8 +11076,9 @@
       <c r="U144" s="2"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-    </row>
-    <row r="145" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X144" s="2"/>
+    </row>
+    <row r="145" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B145" s="4"/>
       <c r="K145" s="5"/>
       <c r="L145" s="2"/>
@@ -10659,8 +11093,9 @@
       <c r="U145" s="2"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-    </row>
-    <row r="146" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X145" s="2"/>
+    </row>
+    <row r="146" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B146" s="4"/>
       <c r="K146" s="5"/>
       <c r="L146" s="2"/>
@@ -10675,8 +11110,9 @@
       <c r="U146" s="2"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-    </row>
-    <row r="147" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X146" s="2"/>
+    </row>
+    <row r="147" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B147" s="4"/>
       <c r="K147" s="5"/>
       <c r="L147" s="2"/>
@@ -10691,8 +11127,9 @@
       <c r="U147" s="2"/>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
-    </row>
-    <row r="148" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X147" s="2"/>
+    </row>
+    <row r="148" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B148" s="18"/>
       <c r="K148" s="6"/>
       <c r="L148" s="2"/>
@@ -10707,8 +11144,9 @@
       <c r="U148" s="2"/>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
-    </row>
-    <row r="149" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X148" s="2"/>
+    </row>
+    <row r="149" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B149" s="18"/>
       <c r="H149" s="8"/>
       <c r="K149" s="5"/>
@@ -10724,8 +11162,9 @@
       <c r="U149" s="2"/>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
-    </row>
-    <row r="150" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X149" s="2"/>
+    </row>
+    <row r="150" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B150" s="18"/>
       <c r="H150" s="8"/>
       <c r="K150" s="5"/>
@@ -10741,8 +11180,9 @@
       <c r="U150" s="2"/>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
-    </row>
-    <row r="151" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X150" s="2"/>
+    </row>
+    <row r="151" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B151" s="18"/>
       <c r="H151" s="8"/>
       <c r="K151" s="5"/>
@@ -10758,8 +11198,9 @@
       <c r="U151" s="2"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-    </row>
-    <row r="152" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X151" s="2"/>
+    </row>
+    <row r="152" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B152" s="18"/>
       <c r="H152" s="8"/>
       <c r="K152" s="5"/>
@@ -10775,8 +11216,9 @@
       <c r="U152" s="2"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-    </row>
-    <row r="153" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X152" s="2"/>
+    </row>
+    <row r="153" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B153" s="18"/>
       <c r="H153" s="8"/>
       <c r="K153" s="5"/>
@@ -10792,8 +11234,9 @@
       <c r="U153" s="2"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-    </row>
-    <row r="154" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X153" s="2"/>
+    </row>
+    <row r="154" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B154" s="18"/>
       <c r="H154" s="8"/>
       <c r="K154" s="5"/>
@@ -10809,8 +11252,9 @@
       <c r="U154" s="2"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-    </row>
-    <row r="155" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X154" s="2"/>
+    </row>
+    <row r="155" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
@@ -10827,8 +11271,9 @@
       <c r="U155" s="2"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-    </row>
-    <row r="156" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X155" s="2"/>
+    </row>
+    <row r="156" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
@@ -10845,8 +11290,9 @@
       <c r="U156" s="2"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-    </row>
-    <row r="157" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X156" s="2"/>
+    </row>
+    <row r="157" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
@@ -10863,8 +11309,9 @@
       <c r="U157" s="2"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-    </row>
-    <row r="158" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X157" s="2"/>
+    </row>
+    <row r="158" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
       <c r="K158" s="5"/>
@@ -10879,8 +11326,9 @@
       <c r="U158" s="2"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-    </row>
-    <row r="159" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X158" s="2"/>
+    </row>
+    <row r="159" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
       <c r="K159" s="5"/>
@@ -10895,8 +11343,9 @@
       <c r="U159" s="2"/>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
-    </row>
-    <row r="160" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X159" s="2"/>
+    </row>
+    <row r="160" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c r="K160" s="5"/>
@@ -10911,8 +11360,9 @@
       <c r="U160" s="2"/>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
-    </row>
-    <row r="161" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X160" s="2"/>
+    </row>
+    <row r="161" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
       <c r="K161" s="5"/>
@@ -10928,8 +11378,9 @@
       <c r="U161" s="2"/>
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
-    </row>
-    <row r="162" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X161" s="2"/>
+    </row>
+    <row r="162" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
       <c r="K162" s="5"/>
@@ -10945,8 +11396,9 @@
       <c r="U162" s="2"/>
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
-    </row>
-    <row r="163" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X162" s="2"/>
+    </row>
+    <row r="163" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
       <c r="K163" s="5"/>
@@ -10962,8 +11414,9 @@
       <c r="U163" s="2"/>
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
-    </row>
-    <row r="164" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X163" s="2"/>
+    </row>
+    <row r="164" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
       <c r="K164" s="5"/>
@@ -10979,8 +11432,9 @@
       <c r="U164" s="2"/>
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
-    </row>
-    <row r="165" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X164" s="2"/>
+    </row>
+    <row r="165" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="G165" s="8"/>
@@ -10998,8 +11452,9 @@
       <c r="U165" s="2"/>
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
-    </row>
-    <row r="166" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X165" s="2"/>
+    </row>
+    <row r="166" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
       <c r="K166" s="6"/>
@@ -11015,8 +11470,9 @@
       <c r="U166" s="2"/>
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
-    </row>
-    <row r="167" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="X166" s="2"/>
+    </row>
+    <row r="167" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K167" s="5"/>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -11029,7 +11485,7 @@
       <c r="T167" s="2"/>
       <c r="U167" s="2"/>
     </row>
-    <row r="168" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K168" s="5"/>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -11042,7 +11498,7 @@
       <c r="T168" s="2"/>
       <c r="U168" s="2"/>
     </row>
-    <row r="169" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K169" s="5"/>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -11055,7 +11511,7 @@
       <c r="T169" s="2"/>
       <c r="U169" s="2"/>
     </row>
-    <row r="170" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K170" s="5"/>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -11068,7 +11524,7 @@
       <c r="T170" s="2"/>
       <c r="U170" s="2"/>
     </row>
-    <row r="171" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K171" s="5"/>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -11081,7 +11537,7 @@
       <c r="T171" s="2"/>
       <c r="U171" s="2"/>
     </row>
-    <row r="172" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K172" s="5"/>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -11094,7 +11550,7 @@
       <c r="T172" s="2"/>
       <c r="U172" s="2"/>
     </row>
-    <row r="173" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K173" s="5"/>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -11107,7 +11563,7 @@
       <c r="T173" s="2"/>
       <c r="U173" s="2"/>
     </row>
-    <row r="174" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K174" s="5"/>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -11120,7 +11576,7 @@
       <c r="T174" s="2"/>
       <c r="U174" s="2"/>
     </row>
-    <row r="175" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K175" s="5"/>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
@@ -11133,7 +11589,7 @@
       <c r="T175" s="2"/>
       <c r="U175" s="2"/>
     </row>
-    <row r="176" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:24" x14ac:dyDescent="0.3">
       <c r="K176" s="5"/>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -11146,7 +11602,7 @@
       <c r="T176" s="2"/>
       <c r="U176" s="2"/>
     </row>
-    <row r="177" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="177" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K177" s="5"/>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -11159,7 +11615,7 @@
       <c r="T177" s="2"/>
       <c r="U177" s="2"/>
     </row>
-    <row r="178" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="178" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K178" s="6"/>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -11172,7 +11628,7 @@
       <c r="T178" s="2"/>
       <c r="U178" s="2"/>
     </row>
-    <row r="179" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="179" spans="5:24" x14ac:dyDescent="0.3">
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
       <c r="G179" s="8"/>
@@ -11192,7 +11648,7 @@
       <c r="U179" s="2"/>
       <c r="V179" s="2"/>
     </row>
-    <row r="180" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="180" spans="5:24" x14ac:dyDescent="0.3">
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
       <c r="G180" s="8"/>
@@ -11212,7 +11668,7 @@
       <c r="U180" s="2"/>
       <c r="V180" s="2"/>
     </row>
-    <row r="181" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="181" spans="5:24" x14ac:dyDescent="0.3">
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
       <c r="G181" s="8"/>
@@ -11232,7 +11688,7 @@
       <c r="U181" s="2"/>
       <c r="V181" s="2"/>
     </row>
-    <row r="182" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="182" spans="5:24" x14ac:dyDescent="0.3">
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
       <c r="G182" s="8"/>
@@ -11252,7 +11708,7 @@
       <c r="U182" s="2"/>
       <c r="V182" s="2"/>
     </row>
-    <row r="183" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="183" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K183" s="5"/>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -11265,8 +11721,9 @@
       <c r="T183" s="2"/>
       <c r="U183" s="2"/>
       <c r="W183" s="2"/>
-    </row>
-    <row r="184" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X183" s="2"/>
+    </row>
+    <row r="184" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K184" s="5"/>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -11279,8 +11736,9 @@
       <c r="T184" s="2"/>
       <c r="U184" s="2"/>
       <c r="W184" s="2"/>
-    </row>
-    <row r="185" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X184" s="2"/>
+    </row>
+    <row r="185" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K185" s="5"/>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -11293,8 +11751,9 @@
       <c r="T185" s="2"/>
       <c r="U185" s="2"/>
       <c r="W185" s="2"/>
-    </row>
-    <row r="186" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X185" s="2"/>
+    </row>
+    <row r="186" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K186" s="5"/>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -11307,8 +11766,9 @@
       <c r="T186" s="2"/>
       <c r="U186" s="2"/>
       <c r="W186" s="2"/>
-    </row>
-    <row r="187" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X186" s="2"/>
+    </row>
+    <row r="187" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K187" s="5"/>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -11321,8 +11781,9 @@
       <c r="T187" s="2"/>
       <c r="U187" s="2"/>
       <c r="W187" s="2"/>
-    </row>
-    <row r="188" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X187" s="2"/>
+    </row>
+    <row r="188" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K188" s="5"/>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -11335,8 +11796,9 @@
       <c r="T188" s="2"/>
       <c r="U188" s="2"/>
       <c r="W188" s="2"/>
-    </row>
-    <row r="189" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X188" s="2"/>
+    </row>
+    <row r="189" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K189" s="5"/>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -11350,8 +11812,9 @@
       <c r="U189" s="2"/>
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
-    </row>
-    <row r="190" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X189" s="2"/>
+    </row>
+    <row r="190" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K190" s="6"/>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -11365,8 +11828,9 @@
       <c r="U190" s="2"/>
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
-    </row>
-    <row r="191" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X190" s="2"/>
+    </row>
+    <row r="191" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K191" s="6"/>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -11380,8 +11844,9 @@
       <c r="U191" s="2"/>
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
-    </row>
-    <row r="192" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="X191" s="2"/>
+    </row>
+    <row r="192" spans="5:24" x14ac:dyDescent="0.3">
       <c r="K192" s="6"/>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -11395,8 +11860,9 @@
       <c r="U192" s="2"/>
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
-    </row>
-    <row r="193" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X192" s="2"/>
+    </row>
+    <row r="193" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K193" s="5"/>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -11409,8 +11875,9 @@
       <c r="T193" s="2"/>
       <c r="U193" s="2"/>
       <c r="W193" s="2"/>
-    </row>
-    <row r="194" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X193" s="2"/>
+    </row>
+    <row r="194" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K194" s="5"/>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -11424,8 +11891,9 @@
       <c r="U194" s="2"/>
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
-    </row>
-    <row r="195" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X194" s="2"/>
+    </row>
+    <row r="195" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K195" s="5"/>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -11439,8 +11907,9 @@
       <c r="U195" s="2"/>
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
-    </row>
-    <row r="196" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X195" s="2"/>
+    </row>
+    <row r="196" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K196" s="5"/>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -11454,8 +11923,9 @@
       <c r="U196" s="2"/>
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
-    </row>
-    <row r="197" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X196" s="2"/>
+    </row>
+    <row r="197" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K197" s="5"/>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -11469,8 +11939,9 @@
       <c r="U197" s="2"/>
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
-    </row>
-    <row r="198" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X197" s="2"/>
+    </row>
+    <row r="198" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K198" s="5"/>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -11484,8 +11955,9 @@
       <c r="U198" s="2"/>
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
-    </row>
-    <row r="199" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X198" s="2"/>
+    </row>
+    <row r="199" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K199" s="5"/>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -11499,8 +11971,9 @@
       <c r="U199" s="2"/>
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
-    </row>
-    <row r="200" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X199" s="2"/>
+    </row>
+    <row r="200" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K200" s="5"/>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -11513,8 +11986,9 @@
       <c r="U200" s="2"/>
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
-    </row>
-    <row r="201" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X200" s="2"/>
+    </row>
+    <row r="201" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K201" s="5"/>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -11528,8 +12002,9 @@
       <c r="U201" s="2"/>
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
-    </row>
-    <row r="202" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X201" s="2"/>
+    </row>
+    <row r="202" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K202" s="5"/>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -11543,8 +12018,9 @@
       <c r="U202" s="2"/>
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
-    </row>
-    <row r="203" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X202" s="2"/>
+    </row>
+    <row r="203" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K203" s="5"/>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -11558,8 +12034,9 @@
       <c r="U203" s="2"/>
       <c r="V203" s="2"/>
       <c r="W203" s="2"/>
-    </row>
-    <row r="204" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X203" s="2"/>
+    </row>
+    <row r="204" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K204" s="5"/>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -11573,8 +12050,9 @@
       <c r="U204" s="2"/>
       <c r="V204" s="2"/>
       <c r="W204" s="2"/>
-    </row>
-    <row r="205" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X204" s="2"/>
+    </row>
+    <row r="205" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K205" s="5"/>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -11588,8 +12066,9 @@
       <c r="U205" s="2"/>
       <c r="V205" s="2"/>
       <c r="W205" s="2"/>
-    </row>
-    <row r="206" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X205" s="2"/>
+    </row>
+    <row r="206" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K206" s="5"/>
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
@@ -11603,8 +12082,9 @@
       <c r="U206" s="2"/>
       <c r="V206" s="2"/>
       <c r="W206" s="2"/>
-    </row>
-    <row r="207" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X206" s="2"/>
+    </row>
+    <row r="207" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K207" s="5"/>
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
@@ -11618,8 +12098,9 @@
       <c r="U207" s="2"/>
       <c r="V207" s="2"/>
       <c r="W207" s="2"/>
-    </row>
-    <row r="208" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X207" s="2"/>
+    </row>
+    <row r="208" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K208" s="5"/>
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
@@ -11633,8 +12114,9 @@
       <c r="U208" s="2"/>
       <c r="V208" s="2"/>
       <c r="W208" s="2"/>
-    </row>
-    <row r="209" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X208" s="2"/>
+    </row>
+    <row r="209" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K209" s="5"/>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -11648,8 +12130,9 @@
       <c r="U209" s="2"/>
       <c r="V209" s="2"/>
       <c r="W209" s="2"/>
-    </row>
-    <row r="210" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X209" s="2"/>
+    </row>
+    <row r="210" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K210" s="5"/>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -11663,8 +12146,9 @@
       <c r="U210" s="2"/>
       <c r="V210" s="2"/>
       <c r="W210" s="2"/>
-    </row>
-    <row r="211" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X210" s="2"/>
+    </row>
+    <row r="211" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K211" s="5"/>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -11678,8 +12162,9 @@
       <c r="U211" s="2"/>
       <c r="V211" s="2"/>
       <c r="W211" s="2"/>
-    </row>
-    <row r="212" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X211" s="2"/>
+    </row>
+    <row r="212" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K212" s="5"/>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -11693,8 +12178,9 @@
       <c r="U212" s="2"/>
       <c r="V212" s="2"/>
       <c r="W212" s="2"/>
-    </row>
-    <row r="213" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X212" s="2"/>
+    </row>
+    <row r="213" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K213" s="5"/>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -11708,8 +12194,9 @@
       <c r="U213" s="2"/>
       <c r="V213" s="2"/>
       <c r="W213" s="2"/>
-    </row>
-    <row r="214" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X213" s="2"/>
+    </row>
+    <row r="214" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K214" s="5"/>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -11723,8 +12210,9 @@
       <c r="U214" s="2"/>
       <c r="V214" s="2"/>
       <c r="W214" s="2"/>
-    </row>
-    <row r="215" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X214" s="2"/>
+    </row>
+    <row r="215" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K215" s="5"/>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -11738,8 +12226,9 @@
       <c r="U215" s="2"/>
       <c r="V215" s="2"/>
       <c r="W215" s="2"/>
-    </row>
-    <row r="216" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X215" s="2"/>
+    </row>
+    <row r="216" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K216" s="5"/>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -11752,8 +12241,9 @@
       <c r="U216" s="2"/>
       <c r="V216" s="2"/>
       <c r="W216" s="2"/>
-    </row>
-    <row r="217" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X216" s="2"/>
+    </row>
+    <row r="217" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K217" s="5"/>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -11767,8 +12257,9 @@
       <c r="U217" s="2"/>
       <c r="V217" s="2"/>
       <c r="W217" s="2"/>
-    </row>
-    <row r="218" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X217" s="2"/>
+    </row>
+    <row r="218" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K218" s="5"/>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -11782,8 +12273,9 @@
       <c r="U218" s="2"/>
       <c r="V218" s="2"/>
       <c r="W218" s="2"/>
-    </row>
-    <row r="219" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X218" s="2"/>
+    </row>
+    <row r="219" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K219" s="5"/>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -11797,8 +12289,9 @@
       <c r="U219" s="2"/>
       <c r="V219" s="2"/>
       <c r="W219" s="2"/>
-    </row>
-    <row r="220" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X219" s="2"/>
+    </row>
+    <row r="220" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K220" s="6"/>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -11812,8 +12305,9 @@
       <c r="U220" s="2"/>
       <c r="V220" s="2"/>
       <c r="W220" s="2"/>
-    </row>
-    <row r="221" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X220" s="2"/>
+    </row>
+    <row r="221" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K221" s="6"/>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -11827,8 +12321,9 @@
       <c r="U221" s="2"/>
       <c r="V221" s="2"/>
       <c r="W221" s="2"/>
-    </row>
-    <row r="222" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X221" s="2"/>
+    </row>
+    <row r="222" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K222" s="6"/>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -11842,8 +12337,9 @@
       <c r="U222" s="2"/>
       <c r="V222" s="2"/>
       <c r="W222" s="2"/>
-    </row>
-    <row r="223" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X222" s="2"/>
+    </row>
+    <row r="223" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K223" s="6"/>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -11857,8 +12353,9 @@
       <c r="U223" s="2"/>
       <c r="V223" s="2"/>
       <c r="W223" s="2"/>
-    </row>
-    <row r="224" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X223" s="2"/>
+    </row>
+    <row r="224" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K224" s="6"/>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -11872,8 +12369,9 @@
       <c r="U224" s="2"/>
       <c r="V224" s="2"/>
       <c r="W224" s="2"/>
-    </row>
-    <row r="225" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X224" s="2"/>
+    </row>
+    <row r="225" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K225" s="6"/>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -11887,8 +12385,9 @@
       <c r="U225" s="2"/>
       <c r="V225" s="2"/>
       <c r="W225" s="2"/>
-    </row>
-    <row r="226" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X225" s="2"/>
+    </row>
+    <row r="226" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K226" s="6"/>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -11902,8 +12401,9 @@
       <c r="U226" s="2"/>
       <c r="V226" s="2"/>
       <c r="W226" s="2"/>
-    </row>
-    <row r="227" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X226" s="2"/>
+    </row>
+    <row r="227" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K227" s="6"/>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -11917,8 +12417,9 @@
       <c r="U227" s="2"/>
       <c r="V227" s="2"/>
       <c r="W227" s="2"/>
-    </row>
-    <row r="228" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X227" s="2"/>
+    </row>
+    <row r="228" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K228" s="6"/>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -11931,8 +12432,9 @@
       <c r="T228" s="2"/>
       <c r="U228" s="2"/>
       <c r="W228" s="2"/>
-    </row>
-    <row r="229" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X228" s="2"/>
+    </row>
+    <row r="229" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K229" s="6"/>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -11946,8 +12448,9 @@
       <c r="U229" s="2"/>
       <c r="V229" s="2"/>
       <c r="W229" s="2"/>
-    </row>
-    <row r="230" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X229" s="2"/>
+    </row>
+    <row r="230" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K230" s="6"/>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -11961,8 +12464,9 @@
       <c r="U230" s="2"/>
       <c r="V230" s="2"/>
       <c r="W230" s="2"/>
-    </row>
-    <row r="231" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X230" s="2"/>
+    </row>
+    <row r="231" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K231" s="6"/>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -11976,8 +12480,9 @@
       <c r="U231" s="2"/>
       <c r="V231" s="2"/>
       <c r="W231" s="2"/>
-    </row>
-    <row r="232" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X231" s="2"/>
+    </row>
+    <row r="232" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K232" s="6"/>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -11991,8 +12496,9 @@
       <c r="U232" s="2"/>
       <c r="V232" s="2"/>
       <c r="W232" s="2"/>
-    </row>
-    <row r="233" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X232" s="2"/>
+    </row>
+    <row r="233" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K233" s="6"/>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -12006,8 +12512,9 @@
       <c r="U233" s="2"/>
       <c r="V233" s="2"/>
       <c r="W233" s="2"/>
-    </row>
-    <row r="234" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X233" s="2"/>
+    </row>
+    <row r="234" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K234" s="6"/>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -12021,8 +12528,9 @@
       <c r="U234" s="2"/>
       <c r="V234" s="2"/>
       <c r="W234" s="2"/>
-    </row>
-    <row r="235" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X234" s="2"/>
+    </row>
+    <row r="235" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K235" s="6"/>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -12036,8 +12544,9 @@
       <c r="U235" s="2"/>
       <c r="V235" s="2"/>
       <c r="W235" s="2"/>
-    </row>
-    <row r="236" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X235" s="2"/>
+    </row>
+    <row r="236" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K236" s="6"/>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -12050,8 +12559,9 @@
       <c r="T236" s="2"/>
       <c r="U236" s="2"/>
       <c r="W236" s="2"/>
-    </row>
-    <row r="237" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X236" s="2"/>
+    </row>
+    <row r="237" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K237" s="6"/>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -12065,8 +12575,9 @@
       <c r="U237" s="2"/>
       <c r="V237" s="2"/>
       <c r="W237" s="2"/>
-    </row>
-    <row r="238" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X237" s="2"/>
+    </row>
+    <row r="238" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K238" s="6"/>
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
@@ -12080,8 +12591,9 @@
       <c r="U238" s="2"/>
       <c r="V238" s="2"/>
       <c r="W238" s="2"/>
-    </row>
-    <row r="239" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X238" s="2"/>
+    </row>
+    <row r="239" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K239" s="6"/>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -12095,8 +12607,9 @@
       <c r="U239" s="2"/>
       <c r="V239" s="2"/>
       <c r="W239" s="2"/>
-    </row>
-    <row r="240" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X239" s="2"/>
+    </row>
+    <row r="240" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K240" s="6"/>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -12110,8 +12623,9 @@
       <c r="U240" s="2"/>
       <c r="V240" s="2"/>
       <c r="W240" s="2"/>
-    </row>
-    <row r="241" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X240" s="2"/>
+    </row>
+    <row r="241" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K241" s="6"/>
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
@@ -12125,8 +12639,9 @@
       <c r="U241" s="2"/>
       <c r="V241" s="2"/>
       <c r="W241" s="2"/>
-    </row>
-    <row r="242" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X241" s="2"/>
+    </row>
+    <row r="242" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K242" s="6"/>
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
@@ -12140,8 +12655,9 @@
       <c r="U242" s="2"/>
       <c r="V242" s="2"/>
       <c r="W242" s="2"/>
-    </row>
-    <row r="243" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X242" s="2"/>
+    </row>
+    <row r="243" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K243" s="6"/>
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
@@ -12155,8 +12671,9 @@
       <c r="U243" s="2"/>
       <c r="V243" s="2"/>
       <c r="W243" s="2"/>
-    </row>
-    <row r="244" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X243" s="2"/>
+    </row>
+    <row r="244" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K244" s="6"/>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -12169,8 +12686,9 @@
       <c r="T244" s="2"/>
       <c r="U244" s="2"/>
       <c r="W244" s="2"/>
-    </row>
-    <row r="245" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X244" s="2"/>
+    </row>
+    <row r="245" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K245" s="6"/>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -12183,8 +12701,9 @@
       <c r="T245" s="2"/>
       <c r="U245" s="2"/>
       <c r="W245" s="2"/>
-    </row>
-    <row r="246" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X245" s="2"/>
+    </row>
+    <row r="246" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K246" s="6"/>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -12197,8 +12716,9 @@
       <c r="U246" s="2"/>
       <c r="V246" s="2"/>
       <c r="W246" s="2"/>
-    </row>
-    <row r="247" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X246" s="2"/>
+    </row>
+    <row r="247" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K247" s="6"/>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -12212,8 +12732,9 @@
       <c r="U247" s="2"/>
       <c r="V247" s="2"/>
       <c r="W247" s="2"/>
-    </row>
-    <row r="248" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X247" s="2"/>
+    </row>
+    <row r="248" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K248" s="6"/>
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
@@ -12227,8 +12748,9 @@
       <c r="U248" s="2"/>
       <c r="V248" s="2"/>
       <c r="W248" s="2"/>
-    </row>
-    <row r="249" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X248" s="2"/>
+    </row>
+    <row r="249" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K249" s="6"/>
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
@@ -12242,8 +12764,9 @@
       <c r="U249" s="2"/>
       <c r="V249" s="2"/>
       <c r="W249" s="2"/>
-    </row>
-    <row r="250" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X249" s="2"/>
+    </row>
+    <row r="250" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K250" s="6"/>
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
@@ -12257,8 +12780,9 @@
       <c r="U250" s="2"/>
       <c r="V250" s="2"/>
       <c r="W250" s="2"/>
-    </row>
-    <row r="251" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X250" s="2"/>
+    </row>
+    <row r="251" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K251" s="6"/>
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
@@ -12272,8 +12796,9 @@
       <c r="U251" s="2"/>
       <c r="V251" s="2"/>
       <c r="W251" s="2"/>
-    </row>
-    <row r="252" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X251" s="2"/>
+    </row>
+    <row r="252" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K252" s="6"/>
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
@@ -12286,8 +12811,9 @@
       <c r="T252" s="2"/>
       <c r="U252" s="2"/>
       <c r="W252" s="2"/>
-    </row>
-    <row r="253" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X252" s="2"/>
+    </row>
+    <row r="253" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K253" s="6"/>
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
@@ -12300,8 +12826,9 @@
       <c r="T253" s="2"/>
       <c r="U253" s="2"/>
       <c r="W253" s="2"/>
-    </row>
-    <row r="254" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X253" s="2"/>
+    </row>
+    <row r="254" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K254" s="6"/>
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
@@ -12314,8 +12841,9 @@
       <c r="T254" s="2"/>
       <c r="U254" s="2"/>
       <c r="W254" s="2"/>
-    </row>
-    <row r="255" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X254" s="2"/>
+    </row>
+    <row r="255" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K255" s="6"/>
       <c r="L255" s="2"/>
       <c r="M255" s="2"/>
@@ -12328,8 +12856,9 @@
       <c r="T255" s="2"/>
       <c r="U255" s="2"/>
       <c r="W255" s="2"/>
-    </row>
-    <row r="256" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X255" s="2"/>
+    </row>
+    <row r="256" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K256" s="6"/>
       <c r="L256" s="2"/>
       <c r="M256" s="2"/>
@@ -12342,8 +12871,9 @@
       <c r="T256" s="2"/>
       <c r="U256" s="2"/>
       <c r="W256" s="2"/>
-    </row>
-    <row r="257" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X256" s="2"/>
+    </row>
+    <row r="257" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K257" s="6"/>
       <c r="L257" s="2"/>
       <c r="M257" s="2"/>
@@ -12356,8 +12886,9 @@
       <c r="T257" s="2"/>
       <c r="U257" s="2"/>
       <c r="W257" s="2"/>
-    </row>
-    <row r="258" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X257" s="2"/>
+    </row>
+    <row r="258" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K258" s="6"/>
       <c r="L258" s="2"/>
       <c r="M258" s="2"/>
@@ -12371,8 +12902,9 @@
       <c r="U258" s="2"/>
       <c r="V258" s="2"/>
       <c r="W258" s="2"/>
-    </row>
-    <row r="259" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X258" s="2"/>
+    </row>
+    <row r="259" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K259" s="6"/>
       <c r="L259" s="2"/>
       <c r="M259" s="2"/>
@@ -12386,8 +12918,9 @@
       <c r="U259" s="2"/>
       <c r="V259" s="2"/>
       <c r="W259" s="2"/>
-    </row>
-    <row r="260" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X259" s="2"/>
+    </row>
+    <row r="260" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K260" s="6"/>
       <c r="L260" s="2"/>
       <c r="M260" s="2"/>
@@ -12401,8 +12934,9 @@
       <c r="U260" s="2"/>
       <c r="V260" s="2"/>
       <c r="W260" s="2"/>
-    </row>
-    <row r="261" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X260" s="2"/>
+    </row>
+    <row r="261" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K261" s="6"/>
       <c r="L261" s="2"/>
       <c r="M261" s="2"/>
@@ -12416,8 +12950,9 @@
       <c r="U261" s="2"/>
       <c r="V261" s="2"/>
       <c r="W261" s="2"/>
-    </row>
-    <row r="262" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X261" s="2"/>
+    </row>
+    <row r="262" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K262" s="6"/>
       <c r="L262" s="2"/>
       <c r="M262" s="2"/>
@@ -12431,8 +12966,9 @@
       <c r="U262" s="2"/>
       <c r="V262" s="2"/>
       <c r="W262" s="2"/>
-    </row>
-    <row r="263" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X262" s="2"/>
+    </row>
+    <row r="263" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K263" s="5"/>
       <c r="L263" s="2"/>
       <c r="M263" s="2"/>
@@ -12445,8 +12981,9 @@
       <c r="T263" s="2"/>
       <c r="U263" s="2"/>
       <c r="W263" s="2"/>
-    </row>
-    <row r="264" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X263" s="2"/>
+    </row>
+    <row r="264" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K264" s="5"/>
       <c r="L264" s="2"/>
       <c r="M264" s="2"/>
@@ -12459,8 +12996,9 @@
       <c r="T264" s="2"/>
       <c r="U264" s="2"/>
       <c r="W264" s="2"/>
-    </row>
-    <row r="265" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X264" s="2"/>
+    </row>
+    <row r="265" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K265" s="5"/>
       <c r="L265" s="2"/>
       <c r="M265" s="2"/>
@@ -12473,8 +13011,9 @@
       <c r="T265" s="2"/>
       <c r="U265" s="2"/>
       <c r="W265" s="2"/>
-    </row>
-    <row r="266" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X265" s="2"/>
+    </row>
+    <row r="266" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K266" s="5"/>
       <c r="L266" s="2"/>
       <c r="M266" s="2"/>
@@ -12487,8 +13026,9 @@
       <c r="T266" s="2"/>
       <c r="U266" s="2"/>
       <c r="W266" s="2"/>
-    </row>
-    <row r="267" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X266" s="2"/>
+    </row>
+    <row r="267" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K267" s="5"/>
       <c r="L267" s="2"/>
       <c r="M267" s="2"/>
@@ -12502,8 +13042,9 @@
       <c r="U267" s="2"/>
       <c r="V267" s="2"/>
       <c r="W267" s="2"/>
-    </row>
-    <row r="268" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X267" s="2"/>
+    </row>
+    <row r="268" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K268" s="5"/>
       <c r="L268" s="2"/>
       <c r="M268" s="2"/>
@@ -12517,8 +13058,9 @@
       <c r="U268" s="2"/>
       <c r="V268" s="2"/>
       <c r="W268" s="2"/>
-    </row>
-    <row r="269" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X268" s="2"/>
+    </row>
+    <row r="269" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K269" s="5"/>
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
@@ -12532,8 +13074,9 @@
       <c r="U269" s="2"/>
       <c r="V269" s="2"/>
       <c r="W269" s="2"/>
-    </row>
-    <row r="270" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X269" s="2"/>
+    </row>
+    <row r="270" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K270" s="5"/>
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
@@ -12547,8 +13090,9 @@
       <c r="U270" s="2"/>
       <c r="V270" s="2"/>
       <c r="W270" s="2"/>
-    </row>
-    <row r="271" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X270" s="2"/>
+    </row>
+    <row r="271" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K271" s="5"/>
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
@@ -12562,8 +13106,9 @@
       <c r="U271" s="2"/>
       <c r="V271" s="2"/>
       <c r="W271" s="2"/>
-    </row>
-    <row r="272" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X271" s="2"/>
+    </row>
+    <row r="272" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K272" s="5"/>
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
@@ -12577,8 +13122,9 @@
       <c r="U272" s="2"/>
       <c r="V272" s="2"/>
       <c r="W272" s="2"/>
-    </row>
-    <row r="273" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X272" s="2"/>
+    </row>
+    <row r="273" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K273" s="5"/>
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
@@ -12591,8 +13137,9 @@
       <c r="T273" s="2"/>
       <c r="U273" s="2"/>
       <c r="W273" s="2"/>
-    </row>
-    <row r="274" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X273" s="2"/>
+    </row>
+    <row r="274" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K274" s="5"/>
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
@@ -12605,8 +13152,9 @@
       <c r="T274" s="2"/>
       <c r="U274" s="2"/>
       <c r="W274" s="2"/>
-    </row>
-    <row r="275" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X274" s="2"/>
+    </row>
+    <row r="275" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K275" s="5"/>
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
@@ -12619,8 +13167,9 @@
       <c r="T275" s="2"/>
       <c r="U275" s="2"/>
       <c r="W275" s="2"/>
-    </row>
-    <row r="276" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X275" s="2"/>
+    </row>
+    <row r="276" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K276" s="5"/>
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
@@ -12633,8 +13182,9 @@
       <c r="T276" s="2"/>
       <c r="U276" s="2"/>
       <c r="W276" s="2"/>
-    </row>
-    <row r="277" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X276" s="2"/>
+    </row>
+    <row r="277" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K277" s="5"/>
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
@@ -12648,8 +13198,9 @@
       <c r="U277" s="2"/>
       <c r="V277" s="2"/>
       <c r="W277" s="2"/>
-    </row>
-    <row r="278" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X277" s="2"/>
+    </row>
+    <row r="278" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K278" s="5"/>
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
@@ -12663,8 +13214,9 @@
       <c r="U278" s="2"/>
       <c r="V278" s="2"/>
       <c r="W278" s="2"/>
-    </row>
-    <row r="279" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X278" s="2"/>
+    </row>
+    <row r="279" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K279" s="5"/>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -12678,8 +13230,9 @@
       <c r="U279" s="2"/>
       <c r="V279" s="2"/>
       <c r="W279" s="2"/>
-    </row>
-    <row r="280" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X279" s="2"/>
+    </row>
+    <row r="280" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K280" s="5"/>
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
@@ -12693,8 +13246,9 @@
       <c r="U280" s="2"/>
       <c r="V280" s="2"/>
       <c r="W280" s="2"/>
-    </row>
-    <row r="281" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X280" s="2"/>
+    </row>
+    <row r="281" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K281" s="5"/>
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
@@ -12708,8 +13262,9 @@
       <c r="U281" s="2"/>
       <c r="V281" s="2"/>
       <c r="W281" s="2"/>
-    </row>
-    <row r="282" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X281" s="2"/>
+    </row>
+    <row r="282" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K282" s="5"/>
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
@@ -12723,8 +13278,9 @@
       <c r="U282" s="2"/>
       <c r="V282" s="2"/>
       <c r="W282" s="2"/>
-    </row>
-    <row r="283" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X282" s="2"/>
+    </row>
+    <row r="283" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K283" s="5"/>
       <c r="L283" s="2"/>
       <c r="M283" s="2"/>
@@ -12738,8 +13294,9 @@
       <c r="U283" s="2"/>
       <c r="V283" s="2"/>
       <c r="W283" s="2"/>
-    </row>
-    <row r="284" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X283" s="2"/>
+    </row>
+    <row r="284" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K284" s="5"/>
       <c r="L284" s="2"/>
       <c r="M284" s="2"/>
@@ -12753,8 +13310,9 @@
       <c r="U284" s="2"/>
       <c r="V284" s="2"/>
       <c r="W284" s="2"/>
-    </row>
-    <row r="285" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X284" s="2"/>
+    </row>
+    <row r="285" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K285" s="5"/>
       <c r="L285" s="2"/>
       <c r="M285" s="2"/>
@@ -12767,8 +13325,9 @@
       <c r="T285" s="2"/>
       <c r="U285" s="2"/>
       <c r="W285" s="2"/>
-    </row>
-    <row r="286" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X285" s="2"/>
+    </row>
+    <row r="286" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C286" s="8"/>
       <c r="D286" s="8"/>
       <c r="E286" s="8"/>
@@ -12786,8 +13345,9 @@
       <c r="T286" s="8"/>
       <c r="U286" s="8"/>
       <c r="W286" s="8"/>
-    </row>
-    <row r="287" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X286" s="8"/>
+    </row>
+    <row r="287" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C287" s="8"/>
       <c r="D287" s="8"/>
       <c r="E287" s="8"/>
@@ -12805,8 +13365,9 @@
       <c r="T287" s="8"/>
       <c r="U287" s="8"/>
       <c r="W287" s="8"/>
-    </row>
-    <row r="288" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="X287" s="8"/>
+    </row>
+    <row r="288" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K288" s="5"/>
       <c r="L288" s="2"/>
       <c r="M288" s="2"/>
@@ -12819,8 +13380,9 @@
       <c r="T288" s="2"/>
       <c r="U288" s="2"/>
       <c r="W288" s="8"/>
-    </row>
-    <row r="289" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X288" s="8"/>
+    </row>
+    <row r="289" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K289" s="5"/>
       <c r="L289" s="2"/>
       <c r="M289" s="2"/>
@@ -12833,8 +13395,9 @@
       <c r="T289" s="2"/>
       <c r="U289" s="2"/>
       <c r="W289" s="8"/>
-    </row>
-    <row r="290" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X289" s="8"/>
+    </row>
+    <row r="290" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K290" s="5"/>
       <c r="L290" s="2"/>
       <c r="M290" s="2"/>
@@ -12847,8 +13410,9 @@
       <c r="T290" s="2"/>
       <c r="U290" s="2"/>
       <c r="W290" s="8"/>
-    </row>
-    <row r="291" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X290" s="8"/>
+    </row>
+    <row r="291" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K291" s="5"/>
       <c r="L291" s="2"/>
       <c r="M291" s="2"/>
@@ -12862,8 +13426,9 @@
       <c r="U291" s="2"/>
       <c r="V291" s="2"/>
       <c r="W291" s="8"/>
-    </row>
-    <row r="292" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X291" s="8"/>
+    </row>
+    <row r="292" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K292" s="5"/>
       <c r="L292" s="2"/>
       <c r="M292" s="2"/>
@@ -12877,8 +13442,9 @@
       <c r="U292" s="2"/>
       <c r="V292" s="2"/>
       <c r="W292" s="8"/>
-    </row>
-    <row r="293" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X292" s="8"/>
+    </row>
+    <row r="293" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K293" s="5"/>
       <c r="L293" s="2"/>
       <c r="M293" s="2"/>
@@ -12891,8 +13457,9 @@
       <c r="T293" s="2"/>
       <c r="U293" s="2"/>
       <c r="W293" s="8"/>
-    </row>
-    <row r="294" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X293" s="8"/>
+    </row>
+    <row r="294" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K294" s="5"/>
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
@@ -12905,8 +13472,9 @@
       <c r="T294" s="2"/>
       <c r="U294" s="2"/>
       <c r="W294" s="8"/>
-    </row>
-    <row r="295" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X294" s="8"/>
+    </row>
+    <row r="295" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K295" s="5"/>
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
@@ -12919,8 +13487,9 @@
       <c r="T295" s="2"/>
       <c r="U295" s="2"/>
       <c r="W295" s="8"/>
-    </row>
-    <row r="296" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X295" s="8"/>
+    </row>
+    <row r="296" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K296" s="5"/>
       <c r="L296" s="2"/>
       <c r="M296" s="2"/>
@@ -12933,8 +13502,9 @@
       <c r="T296" s="2"/>
       <c r="U296" s="2"/>
       <c r="W296" s="8"/>
-    </row>
-    <row r="297" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X296" s="8"/>
+    </row>
+    <row r="297" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K297" s="5"/>
       <c r="L297" s="2"/>
       <c r="M297" s="2"/>
@@ -12947,8 +13517,9 @@
       <c r="T297" s="2"/>
       <c r="U297" s="2"/>
       <c r="W297" s="8"/>
-    </row>
-    <row r="298" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X297" s="8"/>
+    </row>
+    <row r="298" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K298" s="5"/>
       <c r="L298" s="2"/>
       <c r="M298" s="2"/>
@@ -12961,8 +13532,9 @@
       <c r="T298" s="2"/>
       <c r="U298" s="2"/>
       <c r="W298" s="8"/>
-    </row>
-    <row r="299" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X298" s="8"/>
+    </row>
+    <row r="299" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K299" s="5"/>
       <c r="L299" s="2"/>
       <c r="M299" s="2"/>
@@ -12976,8 +13548,9 @@
       <c r="U299" s="2"/>
       <c r="V299" s="2"/>
       <c r="W299" s="8"/>
-    </row>
-    <row r="300" spans="11:23" x14ac:dyDescent="0.3">
+      <c r="X299" s="8"/>
+    </row>
+    <row r="300" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K300" s="5"/>
       <c r="L300" s="2"/>
       <c r="M300" s="2"/>
@@ -12991,10 +13564,11 @@
       <c r="U300" s="2"/>
       <c r="V300" s="2"/>
       <c r="W300" s="8"/>
+      <c r="X300" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W127" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G136:G144 G146:G300 G2:G134" xr:uid="{58155949-CB1B-48D8-A226-133575A9F708}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
@@ -13009,6 +13583,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C300" xr:uid="{C310BEFD-AB98-4273-AFFC-E63848748976}">
       <formula1>Category</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X127" xr:uid="{32FFA324-3F13-4DBB-A164-60E64D941A9A}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13033,7 +13610,7 @@
     <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -13103,8 +13680,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25</v>
       </c>
@@ -13174,8 +13754,11 @@
       <c r="W2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26</v>
       </c>
@@ -13245,8 +13828,11 @@
       <c r="W3" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>27</v>
       </c>
@@ -13316,8 +13902,11 @@
       <c r="W4" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>65</v>
       </c>
@@ -13387,8 +13976,11 @@
       <c r="W5" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>66</v>
       </c>
@@ -13458,8 +14050,11 @@
       <c r="W6" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>69</v>
       </c>
@@ -13529,8 +14124,11 @@
       <c r="W7" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>70</v>
       </c>
@@ -13600,8 +14198,11 @@
       <c r="W8" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>71</v>
       </c>
@@ -13671,8 +14272,11 @@
       <c r="W9" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>72</v>
       </c>
@@ -13742,8 +14346,11 @@
       <c r="W10" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>73</v>
       </c>
@@ -13813,8 +14420,11 @@
       <c r="W11" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>75</v>
       </c>
@@ -13884,8 +14494,11 @@
       <c r="W12" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>76</v>
       </c>
@@ -13955,8 +14568,11 @@
       <c r="W13" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>77</v>
       </c>
@@ -14026,8 +14642,11 @@
       <c r="W14" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>78</v>
       </c>
@@ -14097,8 +14716,11 @@
       <c r="W15" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>79</v>
       </c>
@@ -14167,6 +14789,9 @@
       </c>
       <c r="W16" s="2" t="s">
         <v>27</v>
+      </c>
+      <c r="X16" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
@@ -14239,6 +14864,9 @@
       <c r="W17" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X17" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -14310,6 +14938,9 @@
       <c r="W18" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X18" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -14381,6 +15012,9 @@
       <c r="W19" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X19" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -14452,6 +15086,9 @@
       <c r="W20" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X20" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -14523,6 +15160,9 @@
       <c r="W21" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X21" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -14594,6 +15234,9 @@
       <c r="W22" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X22" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -14665,6 +15308,9 @@
       <c r="W23" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X23" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -14736,6 +15382,9 @@
       <c r="W24" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X24" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -14807,6 +15456,9 @@
       <c r="W25" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X25" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -14878,6 +15530,9 @@
       <c r="W26" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X26" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -14949,6 +15604,9 @@
       <c r="W27" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X27" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -15020,7 +15678,9 @@
       <c r="W28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="X28" s="2"/>
+      <c r="X28" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
@@ -15092,6 +15752,9 @@
       <c r="W29" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X29" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -15163,6 +15826,9 @@
       <c r="W30" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X30" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
@@ -15234,6 +15900,9 @@
       <c r="W31" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="X31" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -15305,8 +15974,11 @@
       <c r="W32" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X32" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>155</v>
       </c>
@@ -15376,8 +16048,11 @@
       <c r="W33" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>160</v>
       </c>
@@ -15447,8 +16122,11 @@
       <c r="W34" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X34" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>161</v>
       </c>
@@ -15518,8 +16196,11 @@
       <c r="W35" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X35" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>162</v>
       </c>
@@ -15589,8 +16270,11 @@
       <c r="W36" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X36" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>163</v>
       </c>
@@ -15660,8 +16344,11 @@
       <c r="W37" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X37" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>164</v>
       </c>
@@ -15731,8 +16418,11 @@
       <c r="W38" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X38" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>165</v>
       </c>
@@ -15802,25 +16492,85 @@
       <c r="W39" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B40" s="18"/>
-      <c r="F40" s="9"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="2"/>
-      <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X39" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>166</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" t="s">
+        <v>41</v>
+      </c>
+      <c r="H40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I40" t="s">
+        <v>271</v>
+      </c>
+      <c r="J40" t="s">
+        <v>272</v>
+      </c>
+      <c r="K40" s="6">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="X40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B41" s="18"/>
       <c r="K41" s="6"/>
       <c r="L41" s="2"/>
@@ -15836,7 +16586,7 @@
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B42" s="18"/>
       <c r="K42" s="6"/>
       <c r="L42" s="2"/>
@@ -15852,7 +16602,7 @@
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B43" s="18"/>
       <c r="K43" s="5"/>
       <c r="L43" s="2"/>
@@ -15868,7 +16618,7 @@
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B44" s="18"/>
       <c r="K44" s="5"/>
       <c r="L44" s="2"/>
@@ -15884,7 +16634,7 @@
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="G45" s="10"/>
       <c r="K45" s="5"/>
       <c r="L45" s="2"/>
@@ -15900,7 +16650,7 @@
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B46" s="20"/>
       <c r="H46" s="9"/>
       <c r="K46" s="5"/>
@@ -15917,7 +16667,7 @@
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B47" s="20"/>
       <c r="H47" s="9"/>
       <c r="I47" s="8"/>
@@ -15935,7 +16685,7 @@
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B48" s="21"/>
       <c r="H48" s="9"/>
       <c r="I48" s="8"/>
@@ -16527,18 +17277,33 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:W86" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F86 G49" xr:uid="{EFD74BD8-58C9-4ACB-93B3-5302AF9CB479}">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G49 F2:F39 F41:F86" xr:uid="{EFD74BD8-58C9-4ACB-93B3-5302AF9CB479}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E86" xr:uid="{5A94C40F-36D4-4CEE-8D35-4A3427FA8283}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E39 D41:E86" xr:uid="{5A94C40F-36D4-4CEE-8D35-4A3427FA8283}">
       <formula1>INDIRECT(C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C86" xr:uid="{BF2AFAAE-B6D2-412A-B5FA-591E8B15DA0C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C39 C41:C86" xr:uid="{BF2AFAAE-B6D2-412A-B5FA-591E8B15DA0C}">
       <formula1>Category</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G48 G50:G86" xr:uid="{4875B19E-87F5-497F-BC8F-1473FB197838}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50:G86 G2:G39 G41:G48" xr:uid="{4875B19E-87F5-497F-BC8F-1473FB197838}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D40:E40" xr:uid="{F281DB64-B057-4B9D-88E7-CEBF330016B4}">
+      <formula1>INDIRECT(C40)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C40" xr:uid="{8AF40484-A1AE-4C22-B2A5-1ED4673DF3F0}">
+      <formula1>Category</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G40" xr:uid="{08E01B60-D280-47DA-B1AC-9B4053DC4068}">
+      <formula1>INDIRECT(D40 &amp; "_size")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F40" xr:uid="{98D46CE6-99BF-4B6F-BB76-EA9504572237}">
+      <formula1>INDIRECT(D40&amp;"_material")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X40" xr:uid="{B1BB9652-FF15-47FB-8099-A047B428E926}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16634,6 +17399,9 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="2" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
@@ -16704,6 +17472,9 @@
       </c>
       <c r="W2" s="14" t="s">
         <v>27</v>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -16790,7 +17561,7 @@
       <c r="W7" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F7" xr:uid="{049F1F64-FDBE-45B5-B292-C2C5EC3F1001}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
@@ -16802,6 +17573,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G7" xr:uid="{A54186C2-8BD9-4A1F-9A77-54DD56F0EC69}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2" xr:uid="{40D6912C-FB6C-4902-8072-EC61FD59EB1C}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16946,7 +17720,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E46FE8D-6B9D-4019-AD13-4A9515E01ECE}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -16957,10 +17731,10 @@
     <col min="8" max="8" width="23.6640625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="55" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -17024,8 +17798,11 @@
       <c r="U1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -17089,8 +17866,11 @@
       <c r="U2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -17154,8 +17934,11 @@
       <c r="U3" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -17219,8 +18002,11 @@
       <c r="U4" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -17284,8 +18070,11 @@
       <c r="U5" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -17349,8 +18138,11 @@
       <c r="U6" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -17414,8 +18206,11 @@
       <c r="U7" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -17479,8 +18274,11 @@
       <c r="U8" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -17544,8 +18342,11 @@
       <c r="U9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -17609,8 +18410,11 @@
       <c r="U10" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -17674,8 +18478,11 @@
       <c r="U11" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -17739,8 +18546,11 @@
       <c r="U12" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -17804,8 +18614,11 @@
       <c r="U13" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -17869,8 +18682,11 @@
       <c r="U14" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -17934,8 +18750,11 @@
       <c r="U15" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -17999,8 +18818,11 @@
       <c r="U16" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -18064,8 +18886,11 @@
       <c r="U17" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -18129,39 +18954,42 @@
       <c r="U18" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S19" s="2"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S20" s="2"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S26" s="2"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S27" s="2"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="S29" s="2"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E15" xr:uid="{2B6F0BAE-1307-4B1B-90C6-C1D65D2741DA}">
       <formula1>INDIRECT(D3 &amp; "_specs")</formula1>
     </dataValidation>
@@ -18170,6 +18998,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F16" xr:uid="{562E144E-2576-46E1-B76C-317B450EC952}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V18" xr:uid="{BBC78778-A7EA-4A99-AE3D-52A4F5B4B708}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
